--- a/Captivi Master Speadsheet.xlsx
+++ b/Captivi Master Speadsheet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gordie/Documents/Academic/Academic_Projects/sna_project-Marguerite/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gordie/Documents/Academic/Academic_Projects/Plautus_SNA-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D558F55-52DC-D646-94C0-EE48D9A23E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
